--- a/Excel/Case Study 3(Pivot Table).xlsx
+++ b/Excel/Case Study 3(Pivot Table).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85DE321D-4700-47D1-BD2C-04187AA3A2D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99031AB0-DD7F-4139-95EC-88190E254FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="26" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -533,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -600,7 +600,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -622,40 +621,6 @@
   <dxfs count="17">
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1078,13 +1043,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -1097,6 +1055,47 @@
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -16340,7 +16339,223 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7ECC409F-1C5F-4108-8369-9AB57BA89342}" name="PivotTable16" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1F4880FF-3315-4216-A872-F2B7F00E655D}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D26:E31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="166" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Bonus %" fld="8" subtotal="average" baseField="2" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{77D2F12D-10FD-4DD9-8940-4834B19C3A57}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D90:E111" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="166" showAll="0">
+      <items count="38">
+        <item h="1" x="1"/>
+        <item h="1" x="17"/>
+        <item h="1" x="5"/>
+        <item h="1" x="3"/>
+        <item h="1" x="24"/>
+        <item h="1" x="6"/>
+        <item h="1" x="4"/>
+        <item h="1" x="19"/>
+        <item h="1" x="15"/>
+        <item h="1" x="8"/>
+        <item h="1" x="28"/>
+        <item h="1" x="0"/>
+        <item h="1" x="26"/>
+        <item h="1" x="35"/>
+        <item h="1" x="10"/>
+        <item h="1" x="33"/>
+        <item h="1" x="2"/>
+        <item x="11"/>
+        <item x="31"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="36"/>
+        <item x="27"/>
+        <item x="25"/>
+        <item x="12"/>
+        <item x="20"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="29"/>
+        <item x="16"/>
+        <item x="22"/>
+        <item x="32"/>
+        <item x="21"/>
+        <item x="34"/>
+        <item x="30"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="21">
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Age" fld="5" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7ECC409F-1C5F-4108-8369-9AB57BA89342}" name="PivotTable16" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="D331:E339" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -16459,461 +16674,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7ABBAF9-BB9A-437A-955B-53C721A53D03}" name="PivotTable6" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D51:E59" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="3"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Age" fld="5" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DB8393F6-AD6A-4B60-BAD8-EC0ADC8487D5}" name="PivotTable5" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D46:D47" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="12">
-    <pivotField showAll="0">
-      <items count="34">
-        <item x="5"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="3"/>
-        <item x="8"/>
-        <item x="25"/>
-        <item x="2"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="17"/>
-        <item x="16"/>
-        <item x="12"/>
-        <item x="30"/>
-        <item x="6"/>
-        <item x="32"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="19"/>
-        <item x="10"/>
-        <item x="31"/>
-        <item x="29"/>
-        <item x="26"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="0"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="1"/>
-        <item x="22"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Exit Date" fld="11" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96A3BB07-508D-4DC9-BE29-04DA6F3E7B04}" name="PivotTable4" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D35:E42" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="42">
-        <item x="6"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="21"/>
-        <item x="7"/>
-        <item x="23"/>
-        <item h="1" x="11"/>
-        <item h="1" x="24"/>
-        <item h="1" x="29"/>
-        <item h="1" x="8"/>
-        <item h="1" x="25"/>
-        <item h="1" x="9"/>
-        <item h="1" x="17"/>
-        <item h="1" x="31"/>
-        <item h="1" x="38"/>
-        <item h="1" x="28"/>
-        <item h="1" x="12"/>
-        <item h="1" x="34"/>
-        <item h="1" x="19"/>
-        <item h="1" x="18"/>
-        <item h="1" x="15"/>
-        <item h="1" x="30"/>
-        <item h="1" x="40"/>
-        <item h="1" x="35"/>
-        <item h="1" x="37"/>
-        <item h="1" x="2"/>
-        <item h="1" x="10"/>
-        <item h="1" x="27"/>
-        <item h="1" x="26"/>
-        <item h="1" x="36"/>
-        <item h="1" x="0"/>
-        <item h="1" x="16"/>
-        <item h="1" x="4"/>
-        <item h="1" x="32"/>
-        <item h="1" x="1"/>
-        <item h="1" x="33"/>
-        <item h="1" x="22"/>
-        <item h="1" x="39"/>
-        <item h="1" x="20"/>
-        <item h="1" x="14"/>
-        <item h="1" x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Annual Salary" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1F4880FF-3315-4216-A872-F2B7F00E655D}" name="PivotTable3" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D26:E31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="166" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Bonus %" fld="8" subtotal="average" baseField="2" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{942ECBF2-7FEC-420C-AB42-1135F1EBA1B6}" name="PivotTable2" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D18:E22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Job Title" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2DBB0717-C704-49C4-8630-DF228D1E9A95}" name="PivotTable1" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D4:E12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="3"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Annual Salary" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4A0F51F-6E2D-443D-B13E-ADAE597C1D35}" name="PivotTable15" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4A0F51F-6E2D-443D-B13E-ADAE597C1D35}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="D241:E326" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -17295,8 +17057,169 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3CB48098-1F17-48C6-BD4B-FCDD74BFE15D}" name="PivotTable14" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96A3BB07-508D-4DC9-BE29-04DA6F3E7B04}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D35:E42" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="42">
+        <item x="6"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="21"/>
+        <item x="7"/>
+        <item x="23"/>
+        <item h="1" x="11"/>
+        <item h="1" x="24"/>
+        <item h="1" x="29"/>
+        <item h="1" x="8"/>
+        <item h="1" x="25"/>
+        <item h="1" x="9"/>
+        <item h="1" x="17"/>
+        <item h="1" x="31"/>
+        <item h="1" x="38"/>
+        <item h="1" x="28"/>
+        <item h="1" x="12"/>
+        <item h="1" x="34"/>
+        <item h="1" x="19"/>
+        <item h="1" x="18"/>
+        <item h="1" x="15"/>
+        <item h="1" x="30"/>
+        <item h="1" x="40"/>
+        <item h="1" x="35"/>
+        <item h="1" x="37"/>
+        <item h="1" x="2"/>
+        <item h="1" x="10"/>
+        <item h="1" x="27"/>
+        <item h="1" x="26"/>
+        <item h="1" x="36"/>
+        <item h="1" x="0"/>
+        <item h="1" x="16"/>
+        <item h="1" x="4"/>
+        <item h="1" x="32"/>
+        <item h="1" x="1"/>
+        <item h="1" x="33"/>
+        <item h="1" x="22"/>
+        <item h="1" x="39"/>
+        <item h="1" x="20"/>
+        <item h="1" x="14"/>
+        <item h="1" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Annual Salary" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C5F28FD-06DE-4811-9C15-02F0C5050334}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D83:E86" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Exit Date" fld="11" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3CB48098-1F17-48C6-BD4B-FCDD74BFE15D}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="D194:E236" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -17506,8 +17429,262 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{21BE3F26-ECFD-48DC-9612-73B6DBE82443}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D75:F79" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="8">
+        <item h="1" x="3"/>
+        <item h="1" x="5"/>
+        <item h="1" x="1"/>
+        <item h="1" x="4"/>
+        <item x="0"/>
+        <item h="1" x="6"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Annual Salary" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{942ECBF2-7FEC-420C-AB42-1135F1EBA1B6}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D18:E22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Job Title" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{099AE6E7-85DA-4C1B-9ACC-BAD084EEB1AF}" name="PivotTable13" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE2EEA24-A914-4D52-8936-2923B85E22CC}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D63:E71" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0" sortType="descending">
+      <items count="34">
+        <item x="5"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="25"/>
+        <item x="2"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="12"/>
+        <item x="30"/>
+        <item x="6"/>
+        <item x="32"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="19"/>
+        <item x="10"/>
+        <item x="31"/>
+        <item x="29"/>
+        <item x="26"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="0"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="1"/>
+        <item x="22"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Max of Annual Salary" fld="7" subtotal="max" baseField="1" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{099AE6E7-85DA-4C1B-9ACC-BAD084EEB1AF}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="D126:H189" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -18706,8 +18883,158 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F6AD529D-8480-40BB-A39B-F7EE06C92E9F}" name="PivotTable12" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7ABBAF9-BB9A-437A-955B-53C721A53D03}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D51:E59" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Age" fld="5" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2DBB0717-C704-49C4-8630-DF228D1E9A95}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D4:E12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Annual Salary" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F6AD529D-8480-40BB-A39B-F7EE06C92E9F}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="D116:G122" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -18786,293 +19113,11 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{77D2F12D-10FD-4DD9-8940-4834B19C3A57}" name="PivotTable11" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D90:E111" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DB8393F6-AD6A-4B60-BAD8-EC0ADC8487D5}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D46:D47" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="166" showAll="0">
-      <items count="38">
-        <item h="1" x="1"/>
-        <item h="1" x="17"/>
-        <item h="1" x="5"/>
-        <item h="1" x="3"/>
-        <item h="1" x="24"/>
-        <item h="1" x="6"/>
-        <item h="1" x="4"/>
-        <item h="1" x="19"/>
-        <item h="1" x="15"/>
-        <item h="1" x="8"/>
-        <item h="1" x="28"/>
-        <item h="1" x="0"/>
-        <item h="1" x="26"/>
-        <item h="1" x="35"/>
-        <item h="1" x="10"/>
-        <item h="1" x="33"/>
-        <item h="1" x="2"/>
-        <item x="11"/>
-        <item x="31"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="36"/>
-        <item x="27"/>
-        <item x="25"/>
-        <item x="12"/>
-        <item x="20"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="18"/>
-        <item x="29"/>
-        <item x="16"/>
-        <item x="22"/>
-        <item x="32"/>
-        <item x="21"/>
-        <item x="34"/>
-        <item x="30"/>
-        <item x="23"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="8"/>
-  </rowFields>
-  <rowItems count="21">
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
-      <x v="36"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Age" fld="5" subtotal="average" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="0">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="8" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C5F28FD-06DE-4811-9C15-02F0C5050334}" name="PivotTable10" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D83:E86" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Exit Date" fld="11" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{21BE3F26-ECFD-48DC-9612-73B6DBE82443}" name="PivotTable9" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D75:F79" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="8">
-        <item h="1" x="3"/>
-        <item h="1" x="5"/>
-        <item h="1" x="1"/>
-        <item h="1" x="4"/>
-        <item x="0"/>
-        <item h="1" x="6"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Annual Salary" fld="7" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE2EEA24-A914-4D52-8936-2923B85E22CC}" name="PivotTable8" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="D63:E71" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0" sortType="descending">
+    <pivotField showAll="0">
       <items count="34">
         <item x="5"/>
         <item x="7"/>
@@ -19109,73 +19154,27 @@
         <item x="9"/>
         <item t="default"/>
       </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="3"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField numFmtId="166" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
   </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
+  <rowItems count="1">
+    <i/>
   </rowItems>
   <colItems count="1">
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Max of Annual Salary" fld="7" subtotal="max" baseField="1" baseItem="0" numFmtId="165"/>
+    <dataField name="Count of Exit Date" fld="11" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -19190,24 +19189,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{606E6FB8-7A99-4F8C-9CC9-583611EADE01}" name="Emp" displayName="Emp" ref="A1:L1001" totalsRowShown="0" headerRowDxfId="1" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{606E6FB8-7A99-4F8C-9CC9-583611EADE01}" name="Emp" displayName="Emp" ref="A1:L1001" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15" tableBorderDxfId="14" totalsRowBorderDxfId="13">
   <autoFilter ref="A1:L1001" xr:uid="{606E6FB8-7A99-4F8C-9CC9-583611EADE01}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L1001">
     <sortCondition ref="F2:F1001"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{A288BF72-58DE-4E37-A3EF-210C09C89051}" name="Job Title" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{EC6E4C7C-A477-45F9-9591-11909D98BDE7}" name="Department" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{FB9FC0B9-67EE-448C-9B3D-BB0DE0CEDD22}" name="Business Unit" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{07E22346-3CDF-4F76-9FB4-2D4C1A71E325}" name="Gender" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{95D73BE3-7A48-41FC-974E-7F8349914389}" name="Ethnicity" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{14B81A6F-BA74-4731-A12D-EC4FCADB499F}" name="Age" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{7FFE585D-4588-4F2A-9E67-37F5AA268517}" name="Hire Date" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{B8C614ED-0F0E-4C66-BAC2-4C4398C67F1F}" name="Annual Salary" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{A52812C7-2B46-4D25-9BDE-CDF86CE389F0}" name="Bonus %" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{9CBBE705-8E43-4F51-81E0-812B1B3973F7}" name="Country" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{E0062919-2BD3-4DAF-85B1-D192C755ABDF}" name="City" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{83B65CAE-A6BB-4369-9FA4-5EEA6C85A1B7}" name="Exit Date" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{A288BF72-58DE-4E37-A3EF-210C09C89051}" name="Job Title" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{EC6E4C7C-A477-45F9-9591-11909D98BDE7}" name="Department" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{FB9FC0B9-67EE-448C-9B3D-BB0DE0CEDD22}" name="Business Unit" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{07E22346-3CDF-4F76-9FB4-2D4C1A71E325}" name="Gender" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{95D73BE3-7A48-41FC-974E-7F8349914389}" name="Ethnicity" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{14B81A6F-BA74-4731-A12D-EC4FCADB499F}" name="Age" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{7FFE585D-4588-4F2A-9E67-37F5AA268517}" name="Hire Date" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{B8C614ED-0F0E-4C66-BAC2-4C4398C67F1F}" name="Annual Salary" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{A52812C7-2B46-4D25-9BDE-CDF86CE389F0}" name="Bonus %" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{9CBBE705-8E43-4F51-81E0-812B1B3973F7}" name="Country" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{E0062919-2BD3-4DAF-85B1-D192C755ABDF}" name="City" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{83B65CAE-A6BB-4369-9FA4-5EEA6C85A1B7}" name="Exit Date" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -72042,7 +72041,7 @@
       <c r="D19" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19">
         <v>139</v>
       </c>
     </row>
@@ -72050,7 +72049,7 @@
       <c r="D20" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20">
         <v>218</v>
       </c>
     </row>
@@ -72058,7 +72057,7 @@
       <c r="D21" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21">
         <v>643</v>
       </c>
     </row>
@@ -72066,7 +72065,7 @@
       <c r="D22" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22">
         <v>1000</v>
       </c>
     </row>
@@ -72090,7 +72089,7 @@
       <c r="D27" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="32">
         <v>0.10236286919831221</v>
       </c>
     </row>
@@ -72098,7 +72097,7 @@
       <c r="D28" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="32">
         <v>7.0408921933085553E-2</v>
       </c>
     </row>
@@ -72106,7 +72105,7 @@
       <c r="D29" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="32">
         <v>8.8646288209606974E-2</v>
       </c>
     </row>
@@ -72114,7 +72113,7 @@
       <c r="D30" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="32">
         <v>9.4943396226415108E-2</v>
       </c>
     </row>
@@ -72122,7 +72121,7 @@
       <c r="D31" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="32">
         <v>8.8660000000000017E-2</v>
       </c>
     </row>
@@ -72199,7 +72198,7 @@
       </c>
     </row>
     <row r="45" spans="3:5" ht="15.6">
-      <c r="C45" s="34">
+      <c r="C45" s="33">
         <v>5</v>
       </c>
       <c r="D45" s="4" t="s">
@@ -72212,12 +72211,12 @@
       </c>
     </row>
     <row r="47" spans="3:5">
-      <c r="D47" s="32">
+      <c r="D47">
         <v>1000</v>
       </c>
     </row>
     <row r="50" spans="3:5" ht="15.6">
-      <c r="C50" s="34">
+      <c r="C50" s="33">
         <v>6</v>
       </c>
       <c r="D50" s="4" t="s">
@@ -72236,7 +72235,7 @@
       <c r="D52" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="E52" s="32">
+      <c r="E52">
         <v>43.65625</v>
       </c>
     </row>
@@ -72244,7 +72243,7 @@
       <c r="D53" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="E53" s="32">
+      <c r="E53">
         <v>45.670886075949369</v>
       </c>
     </row>
@@ -72252,7 +72251,7 @@
       <c r="D54" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54">
         <v>45.291666666666664</v>
       </c>
     </row>
@@ -72260,7 +72259,7 @@
       <c r="D55" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E55" s="32">
+      <c r="E55">
         <v>44.456000000000003</v>
       </c>
     </row>
@@ -72268,7 +72267,7 @@
       <c r="D56" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56">
         <v>44.344398340248965</v>
       </c>
     </row>
@@ -72276,7 +72275,7 @@
       <c r="D57" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57">
         <v>43.216666666666669</v>
       </c>
     </row>
@@ -72284,7 +72283,7 @@
       <c r="D58" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="E58" s="32">
+      <c r="E58">
         <v>43.642857142857146</v>
       </c>
     </row>
@@ -72292,7 +72291,7 @@
       <c r="D59" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="E59" s="32">
+      <c r="E59">
         <v>44.381999999999998</v>
       </c>
     </row>
@@ -72456,7 +72455,7 @@
       <c r="D84" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="E84" s="32">
+      <c r="E84">
         <v>518</v>
       </c>
     </row>
@@ -72464,7 +72463,7 @@
       <c r="D85" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="E85" s="32">
+      <c r="E85">
         <v>482</v>
       </c>
     </row>
@@ -72472,7 +72471,7 @@
       <c r="D86" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="E86" s="32">
+      <c r="E86">
         <v>1000</v>
       </c>
     </row>
@@ -72493,170 +72492,170 @@
       </c>
     </row>
     <row r="91" spans="3:5">
-      <c r="D91" s="35">
+      <c r="D91" s="34">
         <v>0.21</v>
       </c>
-      <c r="E91" s="36">
+      <c r="E91" s="35">
         <v>41</v>
       </c>
     </row>
     <row r="92" spans="3:5">
-      <c r="D92" s="35">
+      <c r="D92" s="34">
         <v>0.22</v>
       </c>
-      <c r="E92" s="36">
+      <c r="E92" s="35">
         <v>35.4</v>
       </c>
     </row>
     <row r="93" spans="3:5">
-      <c r="D93" s="35">
+      <c r="D93" s="34">
         <v>0.23</v>
       </c>
-      <c r="E93" s="36">
+      <c r="E93" s="35">
         <v>43.75</v>
       </c>
     </row>
     <row r="94" spans="3:5">
-      <c r="D94" s="35">
+      <c r="D94" s="34">
         <v>0.24</v>
       </c>
-      <c r="E94" s="36">
+      <c r="E94" s="35">
         <v>51</v>
       </c>
     </row>
     <row r="95" spans="3:5">
-      <c r="D95" s="35">
+      <c r="D95" s="34">
         <v>0.25</v>
       </c>
-      <c r="E95" s="36">
+      <c r="E95" s="35">
         <v>50.333333333333336</v>
       </c>
     </row>
     <row r="96" spans="3:5">
-      <c r="D96" s="35">
+      <c r="D96" s="34">
         <v>0.26</v>
       </c>
-      <c r="E96" s="36">
+      <c r="E96" s="35">
         <v>45.166666666666664</v>
       </c>
     </row>
     <row r="97" spans="4:5">
-      <c r="D97" s="35">
+      <c r="D97" s="34">
         <v>0.27</v>
       </c>
-      <c r="E97" s="36">
+      <c r="E97" s="35">
         <v>38.799999999999997</v>
       </c>
     </row>
     <row r="98" spans="4:5">
-      <c r="D98" s="35">
+      <c r="D98" s="34">
         <v>0.28000000000000003</v>
       </c>
-      <c r="E98" s="36">
+      <c r="E98" s="35">
         <v>43.583333333333336</v>
       </c>
     </row>
     <row r="99" spans="4:5">
-      <c r="D99" s="35">
+      <c r="D99" s="34">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E99" s="36">
+      <c r="E99" s="35">
         <v>38</v>
       </c>
     </row>
     <row r="100" spans="4:5">
-      <c r="D100" s="35">
+      <c r="D100" s="34">
         <v>0.3</v>
       </c>
-      <c r="E100" s="36">
+      <c r="E100" s="35">
         <v>40.421052631578945</v>
       </c>
     </row>
     <row r="101" spans="4:5">
-      <c r="D101" s="35">
+      <c r="D101" s="34">
         <v>0.31</v>
       </c>
-      <c r="E101" s="36">
+      <c r="E101" s="35">
         <v>41.25</v>
       </c>
     </row>
     <row r="102" spans="4:5">
-      <c r="D102" s="35">
+      <c r="D102" s="34">
         <v>0.32</v>
       </c>
-      <c r="E102" s="36">
+      <c r="E102" s="35">
         <v>45.769230769230766</v>
       </c>
     </row>
     <row r="103" spans="4:5">
-      <c r="D103" s="35">
+      <c r="D103" s="34">
         <v>0.33</v>
       </c>
-      <c r="E103" s="36">
+      <c r="E103" s="35">
         <v>43.090909090909093</v>
       </c>
     </row>
     <row r="104" spans="4:5">
-      <c r="D104" s="35">
+      <c r="D104" s="34">
         <v>0.34</v>
       </c>
-      <c r="E104" s="36">
+      <c r="E104" s="35">
         <v>44.111111111111114</v>
       </c>
     </row>
     <row r="105" spans="4:5">
-      <c r="D105" s="35">
+      <c r="D105" s="34">
         <v>0.35</v>
       </c>
-      <c r="E105" s="36">
+      <c r="E105" s="35">
         <v>45</v>
       </c>
     </row>
     <row r="106" spans="4:5">
-      <c r="D106" s="35">
+      <c r="D106" s="34">
         <v>0.36</v>
       </c>
-      <c r="E106" s="36">
+      <c r="E106" s="35">
         <v>43.81818181818182</v>
       </c>
     </row>
     <row r="107" spans="4:5">
-      <c r="D107" s="35">
+      <c r="D107" s="34">
         <v>0.37</v>
       </c>
-      <c r="E107" s="36">
+      <c r="E107" s="35">
         <v>48.142857142857146</v>
       </c>
     </row>
     <row r="108" spans="4:5">
-      <c r="D108" s="35">
+      <c r="D108" s="34">
         <v>0.38</v>
       </c>
-      <c r="E108" s="36">
+      <c r="E108" s="35">
         <v>38.666666666666664</v>
       </c>
     </row>
     <row r="109" spans="4:5">
-      <c r="D109" s="35">
+      <c r="D109" s="34">
         <v>0.39</v>
       </c>
-      <c r="E109" s="36">
+      <c r="E109" s="35">
         <v>44</v>
       </c>
     </row>
     <row r="110" spans="4:5">
-      <c r="D110" s="35">
+      <c r="D110" s="34">
         <v>0.4</v>
       </c>
-      <c r="E110" s="36">
+      <c r="E110" s="35">
         <v>47.875</v>
       </c>
     </row>
     <row r="111" spans="4:5">
-      <c r="D111" s="35" t="s">
+      <c r="D111" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="E111" s="32">
+      <c r="E111">
         <v>43.5</v>
       </c>
     </row>
@@ -72794,816 +72793,696 @@
       </c>
     </row>
     <row r="128" spans="3:8">
-      <c r="D128" s="37">
+      <c r="D128" s="36">
         <v>43835</v>
       </c>
-      <c r="E128" s="32"/>
-      <c r="F128" s="32"/>
-      <c r="G128" s="32">
+      <c r="G128">
         <v>1</v>
       </c>
-      <c r="H128" s="32">
+      <c r="H128">
         <v>1</v>
       </c>
     </row>
     <row r="129" spans="4:8">
-      <c r="D129" s="37">
+      <c r="D129" s="36">
         <v>43843</v>
       </c>
-      <c r="E129" s="32"/>
-      <c r="F129" s="32"/>
-      <c r="G129" s="32">
+      <c r="G129">
         <v>1</v>
       </c>
-      <c r="H129" s="32">
+      <c r="H129">
         <v>1</v>
       </c>
     </row>
     <row r="130" spans="4:8">
-      <c r="D130" s="37">
+      <c r="D130" s="36">
         <v>43844</v>
       </c>
-      <c r="E130" s="32"/>
-      <c r="F130" s="32"/>
-      <c r="G130" s="32">
+      <c r="G130">
         <v>1</v>
       </c>
-      <c r="H130" s="32">
+      <c r="H130">
         <v>1</v>
       </c>
     </row>
     <row r="131" spans="4:8">
-      <c r="D131" s="37">
+      <c r="D131" s="36">
         <v>43847</v>
       </c>
-      <c r="E131" s="32"/>
-      <c r="F131" s="32"/>
-      <c r="G131" s="32">
+      <c r="G131">
         <v>1</v>
       </c>
-      <c r="H131" s="32">
+      <c r="H131">
         <v>1</v>
       </c>
     </row>
     <row r="132" spans="4:8">
-      <c r="D132" s="37">
+      <c r="D132" s="36">
         <v>43850</v>
       </c>
-      <c r="E132" s="32"/>
-      <c r="F132" s="32"/>
-      <c r="G132" s="32">
+      <c r="G132">
         <v>1</v>
       </c>
-      <c r="H132" s="32">
+      <c r="H132">
         <v>1</v>
       </c>
     </row>
     <row r="133" spans="4:8">
-      <c r="D133" s="37">
+      <c r="D133" s="36">
         <v>43863</v>
       </c>
-      <c r="E133" s="32"/>
-      <c r="F133" s="32">
+      <c r="F133">
         <v>1</v>
       </c>
-      <c r="G133" s="32"/>
-      <c r="H133" s="32">
+      <c r="H133">
         <v>1</v>
       </c>
     </row>
     <row r="134" spans="4:8">
-      <c r="D134" s="37">
+      <c r="D134" s="36">
         <v>43864</v>
       </c>
-      <c r="E134" s="32"/>
-      <c r="F134" s="32"/>
-      <c r="G134" s="32">
+      <c r="G134">
         <v>2</v>
       </c>
-      <c r="H134" s="32">
+      <c r="H134">
         <v>2</v>
       </c>
     </row>
     <row r="135" spans="4:8">
-      <c r="D135" s="37">
+      <c r="D135" s="36">
         <v>43866</v>
       </c>
-      <c r="E135" s="32"/>
-      <c r="F135" s="32"/>
-      <c r="G135" s="32">
+      <c r="G135">
         <v>1</v>
       </c>
-      <c r="H135" s="32">
+      <c r="H135">
         <v>1</v>
       </c>
     </row>
     <row r="136" spans="4:8">
-      <c r="D136" s="37">
+      <c r="D136" s="36">
         <v>43868</v>
       </c>
-      <c r="E136" s="32">
+      <c r="E136">
         <v>1</v>
       </c>
-      <c r="F136" s="32"/>
-      <c r="G136" s="32"/>
-      <c r="H136" s="32">
+      <c r="H136">
         <v>1</v>
       </c>
     </row>
     <row r="137" spans="4:8">
-      <c r="D137" s="37">
+      <c r="D137" s="36">
         <v>43878</v>
       </c>
-      <c r="E137" s="32"/>
-      <c r="F137" s="32">
+      <c r="F137">
         <v>1</v>
       </c>
-      <c r="G137" s="32"/>
-      <c r="H137" s="32">
+      <c r="H137">
         <v>1</v>
       </c>
     </row>
     <row r="138" spans="4:8">
-      <c r="D138" s="37">
+      <c r="D138" s="36">
         <v>43898</v>
       </c>
-      <c r="E138" s="32"/>
-      <c r="F138" s="32"/>
-      <c r="G138" s="32">
+      <c r="G138">
         <v>1</v>
       </c>
-      <c r="H138" s="32">
+      <c r="H138">
         <v>1</v>
       </c>
     </row>
     <row r="139" spans="4:8">
-      <c r="D139" s="37">
+      <c r="D139" s="36">
         <v>43903</v>
       </c>
-      <c r="E139" s="32"/>
-      <c r="F139" s="32"/>
-      <c r="G139" s="32">
+      <c r="G139">
         <v>1</v>
       </c>
-      <c r="H139" s="32">
+      <c r="H139">
         <v>1</v>
       </c>
     </row>
     <row r="140" spans="4:8">
-      <c r="D140" s="37">
+      <c r="D140" s="36">
         <v>43904</v>
       </c>
-      <c r="E140" s="32"/>
-      <c r="F140" s="32"/>
-      <c r="G140" s="32">
+      <c r="G140">
         <v>1</v>
       </c>
-      <c r="H140" s="32">
+      <c r="H140">
         <v>1</v>
       </c>
     </row>
     <row r="141" spans="4:8">
-      <c r="D141" s="37">
+      <c r="D141" s="36">
         <v>43930</v>
       </c>
-      <c r="E141" s="32"/>
-      <c r="F141" s="32"/>
-      <c r="G141" s="32">
+      <c r="G141">
         <v>1</v>
       </c>
-      <c r="H141" s="32">
+      <c r="H141">
         <v>1</v>
       </c>
     </row>
     <row r="142" spans="4:8">
-      <c r="D142" s="37">
+      <c r="D142" s="36">
         <v>43935</v>
       </c>
-      <c r="E142" s="32"/>
-      <c r="F142" s="32"/>
-      <c r="G142" s="32">
+      <c r="G142">
         <v>1</v>
       </c>
-      <c r="H142" s="32">
+      <c r="H142">
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="4:8">
-      <c r="D143" s="37">
+      <c r="D143" s="36">
         <v>43936</v>
       </c>
-      <c r="E143" s="32"/>
-      <c r="F143" s="32"/>
-      <c r="G143" s="32">
+      <c r="G143">
         <v>1</v>
       </c>
-      <c r="H143" s="32">
+      <c r="H143">
         <v>1</v>
       </c>
     </row>
     <row r="144" spans="4:8">
-      <c r="D144" s="37">
+      <c r="D144" s="36">
         <v>43937</v>
       </c>
-      <c r="E144" s="32"/>
-      <c r="F144" s="32">
+      <c r="F144">
         <v>1</v>
       </c>
-      <c r="G144" s="32">
+      <c r="G144">
         <v>1</v>
       </c>
-      <c r="H144" s="32">
+      <c r="H144">
         <v>2</v>
       </c>
     </row>
     <row r="145" spans="4:8">
-      <c r="D145" s="37">
+      <c r="D145" s="36">
         <v>43943</v>
       </c>
-      <c r="E145" s="32"/>
-      <c r="F145" s="32"/>
-      <c r="G145" s="32">
+      <c r="G145">
         <v>1</v>
       </c>
-      <c r="H145" s="32">
+      <c r="H145">
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="4:8">
-      <c r="D146" s="37">
+      <c r="D146" s="36">
         <v>43944</v>
       </c>
-      <c r="E146" s="32"/>
-      <c r="F146" s="32"/>
-      <c r="G146" s="32">
+      <c r="G146">
         <v>1</v>
       </c>
-      <c r="H146" s="32">
+      <c r="H146">
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="4:8">
-      <c r="D147" s="37">
+      <c r="D147" s="36">
         <v>43948</v>
       </c>
-      <c r="E147" s="32"/>
-      <c r="F147" s="32"/>
-      <c r="G147" s="32">
+      <c r="G147">
         <v>1</v>
       </c>
-      <c r="H147" s="32">
+      <c r="H147">
         <v>1</v>
       </c>
     </row>
     <row r="148" spans="4:8">
-      <c r="D148" s="37">
+      <c r="D148" s="36">
         <v>43960</v>
       </c>
-      <c r="E148" s="32"/>
-      <c r="F148" s="32"/>
-      <c r="G148" s="32">
+      <c r="G148">
         <v>1</v>
       </c>
-      <c r="H148" s="32">
+      <c r="H148">
         <v>1</v>
       </c>
     </row>
     <row r="149" spans="4:8">
-      <c r="D149" s="37">
+      <c r="D149" s="36">
         <v>43966</v>
       </c>
-      <c r="E149" s="32">
+      <c r="E149">
         <v>1</v>
       </c>
-      <c r="F149" s="32"/>
-      <c r="G149" s="32"/>
-      <c r="H149" s="32">
+      <c r="H149">
         <v>1</v>
       </c>
     </row>
     <row r="150" spans="4:8">
-      <c r="D150" s="37">
+      <c r="D150" s="36">
         <v>43967</v>
       </c>
-      <c r="E150" s="32"/>
-      <c r="F150" s="32"/>
-      <c r="G150" s="32">
+      <c r="G150">
         <v>1</v>
       </c>
-      <c r="H150" s="32">
+      <c r="H150">
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="4:8">
-      <c r="D151" s="37">
+      <c r="D151" s="36">
         <v>43969</v>
       </c>
-      <c r="E151" s="32"/>
-      <c r="F151" s="32"/>
-      <c r="G151" s="32">
+      <c r="G151">
         <v>1</v>
       </c>
-      <c r="H151" s="32">
+      <c r="H151">
         <v>1</v>
       </c>
     </row>
     <row r="152" spans="4:8">
-      <c r="D152" s="37">
+      <c r="D152" s="36">
         <v>43977</v>
       </c>
-      <c r="E152" s="32"/>
-      <c r="F152" s="32">
+      <c r="F152">
         <v>2</v>
       </c>
-      <c r="G152" s="32"/>
-      <c r="H152" s="32">
+      <c r="H152">
         <v>2</v>
       </c>
     </row>
     <row r="153" spans="4:8">
-      <c r="D153" s="37">
+      <c r="D153" s="36">
         <v>43990</v>
       </c>
-      <c r="E153" s="32"/>
-      <c r="F153" s="32"/>
-      <c r="G153" s="32">
+      <c r="G153">
         <v>1</v>
       </c>
-      <c r="H153" s="32">
+      <c r="H153">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="4:8">
-      <c r="D154" s="37">
+      <c r="D154" s="36">
         <v>43996</v>
       </c>
-      <c r="E154" s="32"/>
-      <c r="F154" s="32"/>
-      <c r="G154" s="32">
+      <c r="G154">
         <v>1</v>
       </c>
-      <c r="H154" s="32">
+      <c r="H154">
         <v>1</v>
       </c>
     </row>
     <row r="155" spans="4:8">
-      <c r="D155" s="37">
+      <c r="D155" s="36">
         <v>43999</v>
       </c>
-      <c r="E155" s="32"/>
-      <c r="F155" s="32">
+      <c r="F155">
         <v>1</v>
       </c>
-      <c r="G155" s="32"/>
-      <c r="H155" s="32">
+      <c r="H155">
         <v>1</v>
       </c>
     </row>
     <row r="156" spans="4:8">
-      <c r="D156" s="37">
+      <c r="D156" s="36">
         <v>44009</v>
       </c>
-      <c r="E156" s="32">
+      <c r="E156">
         <v>1</v>
       </c>
-      <c r="F156" s="32"/>
-      <c r="G156" s="32"/>
-      <c r="H156" s="32">
+      <c r="H156">
         <v>1</v>
       </c>
     </row>
     <row r="157" spans="4:8">
-      <c r="D157" s="37">
+      <c r="D157" s="36">
         <v>44013</v>
       </c>
-      <c r="E157" s="32"/>
-      <c r="F157" s="32"/>
-      <c r="G157" s="32">
+      <c r="G157">
         <v>1</v>
       </c>
-      <c r="H157" s="32">
+      <c r="H157">
         <v>1</v>
       </c>
     </row>
     <row r="158" spans="4:8">
-      <c r="D158" s="37">
+      <c r="D158" s="36">
         <v>44014</v>
       </c>
-      <c r="E158" s="32"/>
-      <c r="F158" s="32"/>
-      <c r="G158" s="32">
+      <c r="G158">
         <v>1</v>
       </c>
-      <c r="H158" s="32">
+      <c r="H158">
         <v>1</v>
       </c>
     </row>
     <row r="159" spans="4:8">
-      <c r="D159" s="37">
+      <c r="D159" s="36">
         <v>44015</v>
       </c>
-      <c r="E159" s="32"/>
-      <c r="F159" s="32"/>
-      <c r="G159" s="32">
+      <c r="G159">
         <v>1</v>
       </c>
-      <c r="H159" s="32">
+      <c r="H159">
         <v>1</v>
       </c>
     </row>
     <row r="160" spans="4:8">
-      <c r="D160" s="37">
+      <c r="D160" s="36">
         <v>44022</v>
       </c>
-      <c r="E160" s="32">
+      <c r="E160">
         <v>1</v>
       </c>
-      <c r="F160" s="32"/>
-      <c r="G160" s="32"/>
-      <c r="H160" s="32">
+      <c r="H160">
         <v>1</v>
       </c>
     </row>
     <row r="161" spans="4:8">
-      <c r="D161" s="37">
+      <c r="D161" s="36">
         <v>44024</v>
       </c>
-      <c r="E161" s="32">
+      <c r="E161">
         <v>1</v>
       </c>
-      <c r="F161" s="32"/>
-      <c r="G161" s="32"/>
-      <c r="H161" s="32">
+      <c r="H161">
         <v>1</v>
       </c>
     </row>
     <row r="162" spans="4:8">
-      <c r="D162" s="37">
+      <c r="D162" s="36">
         <v>44025</v>
       </c>
-      <c r="E162" s="32">
+      <c r="E162">
         <v>1</v>
       </c>
-      <c r="F162" s="32"/>
-      <c r="G162" s="32"/>
-      <c r="H162" s="32">
+      <c r="H162">
         <v>1</v>
       </c>
     </row>
     <row r="163" spans="4:8">
-      <c r="D163" s="37">
+      <c r="D163" s="36">
         <v>44030</v>
       </c>
-      <c r="E163" s="32"/>
-      <c r="F163" s="32"/>
-      <c r="G163" s="32">
+      <c r="G163">
         <v>1</v>
       </c>
-      <c r="H163" s="32">
+      <c r="H163">
         <v>1</v>
       </c>
     </row>
     <row r="164" spans="4:8">
-      <c r="D164" s="37">
+      <c r="D164" s="36">
         <v>44032</v>
       </c>
-      <c r="E164" s="32"/>
-      <c r="F164" s="32"/>
-      <c r="G164" s="32">
+      <c r="G164">
         <v>1</v>
       </c>
-      <c r="H164" s="32">
+      <c r="H164">
         <v>1</v>
       </c>
     </row>
     <row r="165" spans="4:8">
-      <c r="D165" s="37">
+      <c r="D165" s="36">
         <v>44034</v>
       </c>
-      <c r="E165" s="32"/>
-      <c r="F165" s="32"/>
-      <c r="G165" s="32">
+      <c r="G165">
         <v>1</v>
       </c>
-      <c r="H165" s="32">
+      <c r="H165">
         <v>1</v>
       </c>
     </row>
     <row r="166" spans="4:8">
-      <c r="D166" s="37">
+      <c r="D166" s="36">
         <v>44036</v>
       </c>
-      <c r="E166" s="32"/>
-      <c r="F166" s="32">
+      <c r="F166">
         <v>1</v>
       </c>
-      <c r="G166" s="32">
+      <c r="G166">
         <v>1</v>
       </c>
-      <c r="H166" s="32">
+      <c r="H166">
         <v>2</v>
       </c>
     </row>
     <row r="167" spans="4:8">
-      <c r="D167" s="37">
+      <c r="D167" s="36">
         <v>44038</v>
       </c>
-      <c r="E167" s="32"/>
-      <c r="F167" s="32"/>
-      <c r="G167" s="32">
+      <c r="G167">
         <v>1</v>
       </c>
-      <c r="H167" s="32">
+      <c r="H167">
         <v>1</v>
       </c>
     </row>
     <row r="168" spans="4:8">
-      <c r="D168" s="37">
+      <c r="D168" s="36">
         <v>44040</v>
       </c>
-      <c r="E168" s="32"/>
-      <c r="F168" s="32"/>
-      <c r="G168" s="32">
+      <c r="G168">
         <v>1</v>
       </c>
-      <c r="H168" s="32">
+      <c r="H168">
         <v>1</v>
       </c>
     </row>
     <row r="169" spans="4:8">
-      <c r="D169" s="37">
+      <c r="D169" s="36">
         <v>44051</v>
       </c>
-      <c r="E169" s="32"/>
-      <c r="F169" s="32"/>
-      <c r="G169" s="32">
+      <c r="G169">
         <v>1</v>
       </c>
-      <c r="H169" s="32">
+      <c r="H169">
         <v>1</v>
       </c>
     </row>
     <row r="170" spans="4:8">
-      <c r="D170" s="37">
+      <c r="D170" s="36">
         <v>44052</v>
       </c>
-      <c r="E170" s="32"/>
-      <c r="F170" s="32">
+      <c r="F170">
         <v>1</v>
       </c>
-      <c r="G170" s="32"/>
-      <c r="H170" s="32">
+      <c r="H170">
         <v>1</v>
       </c>
     </row>
     <row r="171" spans="4:8">
-      <c r="D171" s="37">
+      <c r="D171" s="36">
         <v>44058</v>
       </c>
-      <c r="E171" s="32"/>
-      <c r="F171" s="32"/>
-      <c r="G171" s="32">
+      <c r="G171">
         <v>1</v>
       </c>
-      <c r="H171" s="32">
+      <c r="H171">
         <v>1</v>
       </c>
     </row>
     <row r="172" spans="4:8">
-      <c r="D172" s="37">
+      <c r="D172" s="36">
         <v>44063</v>
       </c>
-      <c r="E172" s="32"/>
-      <c r="F172" s="32"/>
-      <c r="G172" s="32">
+      <c r="G172">
         <v>1</v>
       </c>
-      <c r="H172" s="32">
+      <c r="H172">
         <v>1</v>
       </c>
     </row>
     <row r="173" spans="4:8">
-      <c r="D173" s="37">
+      <c r="D173" s="36">
         <v>44069</v>
       </c>
-      <c r="E173" s="32">
+      <c r="E173">
         <v>1</v>
       </c>
-      <c r="F173" s="32"/>
-      <c r="G173" s="32"/>
-      <c r="H173" s="32">
+      <c r="H173">
         <v>1</v>
       </c>
     </row>
     <row r="174" spans="4:8">
-      <c r="D174" s="37">
+      <c r="D174" s="36">
         <v>44078</v>
       </c>
-      <c r="E174" s="32"/>
-      <c r="F174" s="32"/>
-      <c r="G174" s="32">
+      <c r="G174">
         <v>1</v>
       </c>
-      <c r="H174" s="32">
+      <c r="H174">
         <v>1</v>
       </c>
     </row>
     <row r="175" spans="4:8">
-      <c r="D175" s="37">
+      <c r="D175" s="36">
         <v>44086</v>
       </c>
-      <c r="E175" s="32"/>
-      <c r="F175" s="32">
+      <c r="F175">
         <v>1</v>
       </c>
-      <c r="G175" s="32"/>
-      <c r="H175" s="32">
+      <c r="H175">
         <v>1</v>
       </c>
     </row>
     <row r="176" spans="4:8">
-      <c r="D176" s="37">
+      <c r="D176" s="36">
         <v>44092</v>
       </c>
-      <c r="E176" s="32"/>
-      <c r="F176" s="32"/>
-      <c r="G176" s="32">
+      <c r="G176">
         <v>1</v>
       </c>
-      <c r="H176" s="32">
+      <c r="H176">
         <v>1</v>
       </c>
     </row>
     <row r="177" spans="4:8">
-      <c r="D177" s="37">
+      <c r="D177" s="36">
         <v>44094</v>
       </c>
-      <c r="E177" s="32">
+      <c r="E177">
         <v>1</v>
       </c>
-      <c r="F177" s="32"/>
-      <c r="G177" s="32"/>
-      <c r="H177" s="32">
+      <c r="H177">
         <v>1</v>
       </c>
     </row>
     <row r="178" spans="4:8">
-      <c r="D178" s="37">
+      <c r="D178" s="36">
         <v>44095</v>
       </c>
-      <c r="E178" s="32"/>
-      <c r="F178" s="32"/>
-      <c r="G178" s="32">
+      <c r="G178">
         <v>1</v>
       </c>
-      <c r="H178" s="32">
+      <c r="H178">
         <v>1</v>
       </c>
     </row>
     <row r="179" spans="4:8">
-      <c r="D179" s="37">
+      <c r="D179" s="36">
         <v>44099</v>
       </c>
-      <c r="E179" s="32">
+      <c r="E179">
         <v>2</v>
       </c>
-      <c r="F179" s="32"/>
-      <c r="G179" s="32"/>
-      <c r="H179" s="32">
+      <c r="H179">
         <v>2</v>
       </c>
     </row>
     <row r="180" spans="4:8">
-      <c r="D180" s="37">
+      <c r="D180" s="36">
         <v>44101</v>
       </c>
-      <c r="E180" s="32"/>
-      <c r="F180" s="32"/>
-      <c r="G180" s="32">
+      <c r="G180">
         <v>1</v>
       </c>
-      <c r="H180" s="32">
+      <c r="H180">
         <v>1</v>
       </c>
     </row>
     <row r="181" spans="4:8">
-      <c r="D181" s="37">
+      <c r="D181" s="36">
         <v>44113</v>
       </c>
-      <c r="E181" s="32"/>
-      <c r="F181" s="32"/>
-      <c r="G181" s="32">
+      <c r="G181">
         <v>1</v>
       </c>
-      <c r="H181" s="32">
+      <c r="H181">
         <v>1</v>
       </c>
     </row>
     <row r="182" spans="4:8">
-      <c r="D182" s="37">
+      <c r="D182" s="36">
         <v>44124</v>
       </c>
-      <c r="E182" s="32"/>
-      <c r="F182" s="32"/>
-      <c r="G182" s="32">
+      <c r="G182">
         <v>1</v>
       </c>
-      <c r="H182" s="32">
+      <c r="H182">
         <v>1</v>
       </c>
     </row>
     <row r="183" spans="4:8">
-      <c r="D183" s="37">
+      <c r="D183" s="36">
         <v>44125</v>
       </c>
-      <c r="E183" s="32"/>
-      <c r="F183" s="32">
+      <c r="F183">
         <v>1</v>
       </c>
-      <c r="G183" s="32"/>
-      <c r="H183" s="32">
+      <c r="H183">
         <v>1</v>
       </c>
     </row>
     <row r="184" spans="4:8">
-      <c r="D184" s="37">
+      <c r="D184" s="36">
         <v>44143</v>
       </c>
-      <c r="E184" s="32"/>
-      <c r="F184" s="32">
+      <c r="F184">
         <v>1</v>
       </c>
-      <c r="G184" s="32"/>
-      <c r="H184" s="32">
+      <c r="H184">
         <v>1</v>
       </c>
     </row>
     <row r="185" spans="4:8">
-      <c r="D185" s="37">
+      <c r="D185" s="36">
         <v>44153</v>
       </c>
-      <c r="E185" s="32"/>
-      <c r="F185" s="32">
+      <c r="F185">
         <v>1</v>
       </c>
-      <c r="G185" s="32"/>
-      <c r="H185" s="32">
+      <c r="H185">
         <v>1</v>
       </c>
     </row>
     <row r="186" spans="4:8">
-      <c r="D186" s="37">
+      <c r="D186" s="36">
         <v>44181</v>
       </c>
-      <c r="E186" s="32">
+      <c r="E186">
         <v>1</v>
       </c>
-      <c r="F186" s="32"/>
-      <c r="G186" s="32"/>
-      <c r="H186" s="32">
+      <c r="H186">
         <v>1</v>
       </c>
     </row>
     <row r="187" spans="4:8">
-      <c r="D187" s="37">
+      <c r="D187" s="36">
         <v>44189</v>
       </c>
-      <c r="E187" s="32"/>
-      <c r="F187" s="32"/>
-      <c r="G187" s="32">
+      <c r="G187">
         <v>1</v>
       </c>
-      <c r="H187" s="32">
+      <c r="H187">
         <v>1</v>
       </c>
     </row>
     <row r="188" spans="4:8">
-      <c r="D188" s="37">
+      <c r="D188" s="36">
         <v>44192</v>
       </c>
-      <c r="E188" s="32">
+      <c r="E188">
         <v>1</v>
       </c>
-      <c r="F188" s="32"/>
-      <c r="G188" s="32"/>
-      <c r="H188" s="32">
+      <c r="H188">
         <v>1</v>
       </c>
     </row>
     <row r="189" spans="4:8">
-      <c r="D189" s="37" t="s">
+      <c r="D189" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="E189" s="32">
+      <c r="E189">
         <v>12</v>
       </c>
-      <c r="F189" s="32">
+      <c r="F189">
         <v>12</v>
       </c>
-      <c r="G189" s="32">
-        <v>42</v>
-      </c>
-      <c r="H189" s="32">
+      <c r="G189">
+        <v>42</v>
+      </c>
+      <c r="H189">
         <v>66</v>
       </c>
     </row>
@@ -73977,671 +73856,671 @@
     </row>
     <row r="242" spans="4:5">
       <c r="D242" s="31"/>
-      <c r="E242" s="33">
+      <c r="E242" s="32">
         <v>8.9759562841530027E-2</v>
       </c>
     </row>
     <row r="243" spans="4:5">
-      <c r="D243" s="38">
+      <c r="D243" s="37">
         <v>34686</v>
       </c>
-      <c r="E243" s="33">
+      <c r="E243" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="244" spans="4:5">
-      <c r="D244" s="38">
+      <c r="D244" s="37">
         <v>35413</v>
       </c>
-      <c r="E244" s="33">
+      <c r="E244" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="245" spans="4:5">
-      <c r="D245" s="38">
+      <c r="D245" s="37">
         <v>36079</v>
       </c>
-      <c r="E245" s="33">
+      <c r="E245" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="246" spans="4:5">
-      <c r="D246" s="38">
+      <c r="D246" s="37">
         <v>37623</v>
       </c>
-      <c r="E246" s="33">
+      <c r="E246" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="247" spans="4:5">
-      <c r="D247" s="38">
+      <c r="D247" s="37">
         <v>38122</v>
       </c>
-      <c r="E247" s="33">
+      <c r="E247" s="32">
         <v>0.09</v>
       </c>
     </row>
     <row r="248" spans="4:5">
-      <c r="D248" s="38">
+      <c r="D248" s="37">
         <v>38131</v>
       </c>
-      <c r="E248" s="33">
+      <c r="E248" s="32">
         <v>0.17</v>
       </c>
     </row>
     <row r="249" spans="4:5">
-      <c r="D249" s="38">
+      <c r="D249" s="37">
         <v>38318</v>
       </c>
-      <c r="E249" s="33">
+      <c r="E249" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="250" spans="4:5">
-      <c r="D250" s="38">
+      <c r="D250" s="37">
         <v>38456</v>
       </c>
-      <c r="E250" s="33">
+      <c r="E250" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="251" spans="4:5">
-      <c r="D251" s="38">
+      <c r="D251" s="37">
         <v>38829</v>
       </c>
-      <c r="E251" s="33">
+      <c r="E251" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="252" spans="4:5">
-      <c r="D252" s="38">
+      <c r="D252" s="37">
         <v>39180</v>
       </c>
-      <c r="E252" s="33">
+      <c r="E252" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="253" spans="4:5">
-      <c r="D253" s="38">
+      <c r="D253" s="37">
         <v>39310</v>
       </c>
-      <c r="E253" s="33">
+      <c r="E253" s="32">
         <v>0.13</v>
       </c>
     </row>
     <row r="254" spans="4:5">
-      <c r="D254" s="38">
+      <c r="D254" s="37">
         <v>39598</v>
       </c>
-      <c r="E254" s="33">
+      <c r="E254" s="32">
         <v>0.24</v>
       </c>
     </row>
     <row r="255" spans="4:5">
-      <c r="D255" s="38">
+      <c r="D255" s="37">
         <v>39616</v>
       </c>
-      <c r="E255" s="33">
+      <c r="E255" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="4:5">
-      <c r="D256" s="38">
+      <c r="D256" s="37">
         <v>40153</v>
       </c>
-      <c r="E256" s="33">
+      <c r="E256" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="257" spans="4:5">
-      <c r="D257" s="38">
+      <c r="D257" s="37">
         <v>40193</v>
       </c>
-      <c r="E257" s="33">
+      <c r="E257" s="32">
         <v>0.15</v>
       </c>
     </row>
     <row r="258" spans="4:5">
-      <c r="D258" s="38">
+      <c r="D258" s="37">
         <v>40903</v>
       </c>
-      <c r="E258" s="33">
+      <c r="E258" s="32">
         <v>0.12</v>
       </c>
     </row>
     <row r="259" spans="4:5">
-      <c r="D259" s="38">
+      <c r="D259" s="37">
         <v>41430</v>
       </c>
-      <c r="E259" s="33">
+      <c r="E259" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="260" spans="4:5">
-      <c r="D260" s="38">
+      <c r="D260" s="37">
         <v>41621</v>
       </c>
-      <c r="E260" s="33">
+      <c r="E260" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="261" spans="4:5">
-      <c r="D261" s="38">
+      <c r="D261" s="37">
         <v>41661</v>
       </c>
-      <c r="E261" s="33">
+      <c r="E261" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="262" spans="4:5">
-      <c r="D262" s="38">
+      <c r="D262" s="37">
         <v>41725</v>
       </c>
-      <c r="E262" s="33">
+      <c r="E262" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="263" spans="4:5">
-      <c r="D263" s="38">
+      <c r="D263" s="37">
         <v>41938</v>
       </c>
-      <c r="E263" s="33">
+      <c r="E263" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="264" spans="4:5">
-      <c r="D264" s="38">
+      <c r="D264" s="37">
         <v>41998</v>
       </c>
-      <c r="E264" s="33">
+      <c r="E264" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="265" spans="4:5">
-      <c r="D265" s="38">
+      <c r="D265" s="37">
         <v>42164</v>
       </c>
-      <c r="E265" s="33">
+      <c r="E265" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="266" spans="4:5">
-      <c r="D266" s="38">
+      <c r="D266" s="37">
         <v>42224</v>
       </c>
-      <c r="E266" s="33">
+      <c r="E266" s="32">
         <v>0.05</v>
       </c>
     </row>
     <row r="267" spans="4:5">
-      <c r="D267" s="38">
+      <c r="D267" s="37">
         <v>42338</v>
       </c>
-      <c r="E267" s="33">
+      <c r="E267" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="268" spans="4:5">
-      <c r="D268" s="38">
+      <c r="D268" s="37">
         <v>42445</v>
       </c>
-      <c r="E268" s="33">
+      <c r="E268" s="32">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="269" spans="4:5">
-      <c r="D269" s="38">
+      <c r="D269" s="37">
         <v>42646</v>
       </c>
-      <c r="E269" s="33">
+      <c r="E269" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="270" spans="4:5">
-      <c r="D270" s="38">
+      <c r="D270" s="37">
         <v>42820</v>
       </c>
-      <c r="E270" s="33">
+      <c r="E270" s="32">
         <v>0.33</v>
       </c>
     </row>
     <row r="271" spans="4:5">
-      <c r="D271" s="38">
+      <c r="D271" s="37">
         <v>42932</v>
       </c>
-      <c r="E271" s="33">
+      <c r="E271" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="272" spans="4:5">
-      <c r="D272" s="38">
+      <c r="D272" s="37">
         <v>42958</v>
       </c>
-      <c r="E272" s="33">
+      <c r="E272" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="273" spans="4:5">
-      <c r="D273" s="38">
+      <c r="D273" s="37">
         <v>43000</v>
       </c>
-      <c r="E273" s="33">
+      <c r="E273" s="32">
         <v>0.15</v>
       </c>
     </row>
     <row r="274" spans="4:5">
-      <c r="D274" s="38">
+      <c r="D274" s="37">
         <v>43003</v>
       </c>
-      <c r="E274" s="33">
+      <c r="E274" s="32">
         <v>0.32</v>
       </c>
     </row>
     <row r="275" spans="4:5">
-      <c r="D275" s="38">
+      <c r="D275" s="37">
         <v>43016</v>
       </c>
-      <c r="E275" s="33">
+      <c r="E275" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="276" spans="4:5">
-      <c r="D276" s="38">
+      <c r="D276" s="37">
         <v>43078</v>
       </c>
-      <c r="E276" s="33">
+      <c r="E276" s="32">
         <v>0.12</v>
       </c>
     </row>
     <row r="277" spans="4:5">
-      <c r="D277" s="38">
+      <c r="D277" s="37">
         <v>43091</v>
       </c>
-      <c r="E277" s="33">
+      <c r="E277" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="278" spans="4:5">
-      <c r="D278" s="38">
+      <c r="D278" s="37">
         <v>43108</v>
       </c>
-      <c r="E278" s="33">
+      <c r="E278" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="279" spans="4:5">
-      <c r="D279" s="38">
+      <c r="D279" s="37">
         <v>43229</v>
       </c>
-      <c r="E279" s="33">
+      <c r="E279" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="280" spans="4:5">
-      <c r="D280" s="38">
+      <c r="D280" s="37">
         <v>43251</v>
       </c>
-      <c r="E280" s="33">
+      <c r="E280" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="281" spans="4:5">
-      <c r="D281" s="38">
+      <c r="D281" s="37">
         <v>43385</v>
       </c>
-      <c r="E281" s="33">
+      <c r="E281" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="282" spans="4:5">
-      <c r="D282" s="38">
+      <c r="D282" s="37">
         <v>43538</v>
       </c>
-      <c r="E282" s="33">
+      <c r="E282" s="32">
         <v>0.09</v>
       </c>
     </row>
     <row r="283" spans="4:5">
-      <c r="D283" s="38">
+      <c r="D283" s="37">
         <v>43558</v>
       </c>
-      <c r="E283" s="33">
+      <c r="E283" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="284" spans="4:5">
-      <c r="D284" s="38">
+      <c r="D284" s="37">
         <v>43594</v>
       </c>
-      <c r="E284" s="33">
+      <c r="E284" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="285" spans="4:5">
-      <c r="D285" s="38">
+      <c r="D285" s="37">
         <v>43608</v>
       </c>
-      <c r="E285" s="33">
+      <c r="E285" s="32">
         <v>0.11</v>
       </c>
     </row>
     <row r="286" spans="4:5">
-      <c r="D286" s="38">
+      <c r="D286" s="37">
         <v>43681</v>
       </c>
-      <c r="E286" s="33">
+      <c r="E286" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="287" spans="4:5">
-      <c r="D287" s="38">
+      <c r="D287" s="37">
         <v>43810</v>
       </c>
-      <c r="E287" s="33">
+      <c r="E287" s="32">
         <v>0.4</v>
       </c>
     </row>
     <row r="288" spans="4:5">
-      <c r="D288" s="38">
+      <c r="D288" s="37">
         <v>43821</v>
       </c>
-      <c r="E288" s="33">
+      <c r="E288" s="32">
         <v>0.1</v>
       </c>
     </row>
     <row r="289" spans="4:5">
-      <c r="D289" s="38">
+      <c r="D289" s="37">
         <v>43865</v>
       </c>
-      <c r="E289" s="33">
+      <c r="E289" s="32">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="290" spans="4:5">
-      <c r="D290" s="38">
+      <c r="D290" s="37">
         <v>43899</v>
       </c>
-      <c r="E290" s="33">
+      <c r="E290" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="291" spans="4:5">
-      <c r="D291" s="38">
+      <c r="D291" s="37">
         <v>43945</v>
       </c>
-      <c r="E291" s="33">
+      <c r="E291" s="32">
         <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="292" spans="4:5">
-      <c r="D292" s="38">
+      <c r="D292" s="37">
         <v>43991</v>
       </c>
-      <c r="E292" s="33">
+      <c r="E292" s="32">
         <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="293" spans="4:5">
-      <c r="D293" s="38">
+      <c r="D293" s="37">
         <v>44020</v>
       </c>
-      <c r="E293" s="33">
+      <c r="E293" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="294" spans="4:5">
-      <c r="D294" s="38">
+      <c r="D294" s="37">
         <v>44024</v>
       </c>
-      <c r="E294" s="33">
+      <c r="E294" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="295" spans="4:5">
-      <c r="D295" s="38">
+      <c r="D295" s="37">
         <v>44029</v>
       </c>
-      <c r="E295" s="33">
+      <c r="E295" s="32">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="296" spans="4:5">
-      <c r="D296" s="38">
+      <c r="D296" s="37">
         <v>44099</v>
       </c>
-      <c r="E296" s="33">
+      <c r="E296" s="32">
         <v>0.22</v>
       </c>
     </row>
     <row r="297" spans="4:5">
-      <c r="D297" s="38">
+      <c r="D297" s="37">
         <v>44107</v>
       </c>
-      <c r="E297" s="33">
+      <c r="E297" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="298" spans="4:5">
-      <c r="D298" s="38">
+      <c r="D298" s="37">
         <v>44177</v>
       </c>
-      <c r="E298" s="33">
+      <c r="E298" s="32">
         <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="299" spans="4:5">
-      <c r="D299" s="38">
+      <c r="D299" s="37">
         <v>44186</v>
       </c>
-      <c r="E299" s="33">
+      <c r="E299" s="32">
         <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="300" spans="4:5">
-      <c r="D300" s="38">
+      <c r="D300" s="37">
         <v>44203</v>
       </c>
-      <c r="E300" s="33">
+      <c r="E300" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="301" spans="4:5">
-      <c r="D301" s="38">
+      <c r="D301" s="37">
         <v>44211</v>
       </c>
-      <c r="E301" s="33">
+      <c r="E301" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="302" spans="4:5">
-      <c r="D302" s="38">
+      <c r="D302" s="37">
         <v>44229</v>
       </c>
-      <c r="E302" s="33">
+      <c r="E302" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="303" spans="4:5">
-      <c r="D303" s="38">
+      <c r="D303" s="37">
         <v>44257</v>
       </c>
-      <c r="E303" s="33">
+      <c r="E303" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="304" spans="4:5">
-      <c r="D304" s="38">
+      <c r="D304" s="37">
         <v>44263</v>
       </c>
-      <c r="E304" s="33">
+      <c r="E304" s="32">
         <v>0.1</v>
       </c>
     </row>
     <row r="305" spans="4:5">
-      <c r="D305" s="38">
+      <c r="D305" s="37">
         <v>44295</v>
       </c>
-      <c r="E305" s="33">
+      <c r="E305" s="32">
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="306" spans="4:5">
-      <c r="D306" s="38">
+      <c r="D306" s="37">
         <v>44306</v>
       </c>
-      <c r="E306" s="33">
+      <c r="E306" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="307" spans="4:5">
-      <c r="D307" s="38">
+      <c r="D307" s="37">
         <v>44317</v>
       </c>
-      <c r="E307" s="33">
+      <c r="E307" s="32">
         <v>0.06</v>
       </c>
     </row>
     <row r="308" spans="4:5">
-      <c r="D308" s="38">
+      <c r="D308" s="37">
         <v>44334</v>
       </c>
-      <c r="E308" s="33">
+      <c r="E308" s="32">
         <v>0.23</v>
       </c>
     </row>
     <row r="309" spans="4:5">
-      <c r="D309" s="38">
+      <c r="D309" s="37">
         <v>44336</v>
       </c>
-      <c r="E309" s="33">
+      <c r="E309" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="310" spans="4:5">
-      <c r="D310" s="38">
+      <c r="D310" s="37">
         <v>44340</v>
       </c>
-      <c r="E310" s="33">
+      <c r="E310" s="32">
         <v>0.08</v>
       </c>
     </row>
     <row r="311" spans="4:5">
-      <c r="D311" s="38">
+      <c r="D311" s="37">
         <v>44371</v>
       </c>
-      <c r="E311" s="33">
+      <c r="E311" s="32">
         <v>0.13</v>
       </c>
     </row>
     <row r="312" spans="4:5">
-      <c r="D312" s="38">
+      <c r="D312" s="37">
         <v>44386</v>
       </c>
-      <c r="E312" s="33">
+      <c r="E312" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="313" spans="4:5">
-      <c r="D313" s="38">
+      <c r="D313" s="37">
         <v>44404</v>
       </c>
-      <c r="E313" s="33">
+      <c r="E313" s="32">
         <v>0.27</v>
       </c>
     </row>
     <row r="314" spans="4:5">
-      <c r="D314" s="38">
+      <c r="D314" s="37">
         <v>44422</v>
       </c>
-      <c r="E314" s="33">
+      <c r="E314" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="315" spans="4:5">
-      <c r="D315" s="38">
+      <c r="D315" s="37">
         <v>44465</v>
       </c>
-      <c r="E315" s="33">
+      <c r="E315" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="316" spans="4:5">
-      <c r="D316" s="38">
+      <c r="D316" s="37">
         <v>44485</v>
       </c>
-      <c r="E316" s="33">
+      <c r="E316" s="32">
         <v>0.15</v>
       </c>
     </row>
     <row r="317" spans="4:5">
-      <c r="D317" s="38">
+      <c r="D317" s="37">
         <v>44491</v>
       </c>
-      <c r="E317" s="33">
+      <c r="E317" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="318" spans="4:5">
-      <c r="D318" s="38">
+      <c r="D318" s="37">
         <v>44510</v>
       </c>
-      <c r="E318" s="33">
+      <c r="E318" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="319" spans="4:5">
-      <c r="D319" s="38">
+      <c r="D319" s="37">
         <v>44661</v>
       </c>
-      <c r="E319" s="33">
+      <c r="E319" s="32">
         <v>0.21</v>
       </c>
     </row>
     <row r="320" spans="4:5">
-      <c r="D320" s="38">
+      <c r="D320" s="37">
         <v>44662</v>
       </c>
-      <c r="E320" s="33">
+      <c r="E320" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="321" spans="3:5">
-      <c r="D321" s="38">
+      <c r="D321" s="37">
         <v>44671</v>
       </c>
-      <c r="E321" s="33">
+      <c r="E321" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="322" spans="3:5">
-      <c r="D322" s="38">
+      <c r="D322" s="37">
         <v>44699</v>
       </c>
-      <c r="E322" s="33">
+      <c r="E322" s="32">
         <v>0.15</v>
       </c>
     </row>
     <row r="323" spans="3:5">
-      <c r="D323" s="38">
+      <c r="D323" s="37">
         <v>44715</v>
       </c>
-      <c r="E323" s="33">
+      <c r="E323" s="32">
         <v>0.11</v>
       </c>
     </row>
     <row r="324" spans="3:5">
-      <c r="D324" s="38">
+      <c r="D324" s="37">
         <v>44732</v>
       </c>
-      <c r="E324" s="33">
+      <c r="E324" s="32">
         <v>0.24</v>
       </c>
     </row>
     <row r="325" spans="3:5">
-      <c r="D325" s="38">
+      <c r="D325" s="37">
         <v>44790</v>
       </c>
-      <c r="E325" s="33">
+      <c r="E325" s="32">
         <v>0.32</v>
       </c>
     </row>
@@ -74649,7 +74528,7 @@
       <c r="D326" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="E326" s="33">
+      <c r="E326" s="32">
         <v>8.8659999999999989E-2</v>
       </c>
     </row>
@@ -74673,7 +74552,7 @@
       <c r="D332" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="E332" s="32">
+      <c r="E332">
         <v>25</v>
       </c>
     </row>
@@ -74681,7 +74560,7 @@
       <c r="D333" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="E333" s="32">
+      <c r="E333">
         <v>25</v>
       </c>
     </row>
@@ -74689,7 +74568,7 @@
       <c r="D334" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E334" s="32">
+      <c r="E334">
         <v>25</v>
       </c>
     </row>
@@ -74697,7 +74576,7 @@
       <c r="D335" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E335" s="32">
+      <c r="E335">
         <v>25</v>
       </c>
     </row>
@@ -74705,7 +74584,7 @@
       <c r="D336" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="E336" s="32">
+      <c r="E336">
         <v>25</v>
       </c>
     </row>
@@ -74713,7 +74592,7 @@
       <c r="D337" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="E337" s="32">
+      <c r="E337">
         <v>25</v>
       </c>
     </row>
@@ -74721,7 +74600,7 @@
       <c r="D338" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="E338" s="32">
+      <c r="E338">
         <v>25</v>
       </c>
     </row>
@@ -74729,7 +74608,7 @@
       <c r="D339" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="E339" s="32">
+      <c r="E339">
         <v>25</v>
       </c>
     </row>
